--- a/Docs/assets to import - final from logistic Nabaa.xlsx
+++ b/Docs/assets to import - final from logistic Nabaa.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\logistic\Docs\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E58C2156-05F4-41EF-86A8-86DD82559411}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BC142B7B-F88A-4ECC-BFE2-4954C89A6B7B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" activeTab="4" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-23148" yWindow="-36" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Furniture" sheetId="1" r:id="rId1"/>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5279" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="5680" uniqueCount="314">
   <si>
     <t>Furniture</t>
   </si>
@@ -812,9 +812,6 @@
     <t xml:space="preserve">hot and cold water dispenser </t>
   </si>
   <si>
-    <t xml:space="preserve"> </t>
-  </si>
-  <si>
     <t>18 (45 cm)</t>
   </si>
   <si>
@@ -972,6 +969,18 @@
   </si>
   <si>
     <t>black Printer</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Owned By </t>
+  </si>
+  <si>
+    <t>B&amp;Z</t>
+  </si>
+  <si>
+    <t xml:space="preserve">LandLord </t>
+  </si>
+  <si>
+    <t>Owned By</t>
   </si>
 </sst>
 </file>
@@ -1019,7 +1028,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="5">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1038,12 +1047,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.39997558519241921"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="1">
     <border>
@@ -1058,7 +1061,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="3" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="17">
+  <cellXfs count="16">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
@@ -1082,7 +1085,6 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="14" fontId="0" fillId="4" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
@@ -1414,7 +1416,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W350"/>
+  <dimension ref="A1:X350"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="4" bestFit="1" customWidth="1"/>
@@ -1429,7 +1431,7 @@
     <col min="20" max="20" width="63.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" ht="13.95" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -1499,8 +1501,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -1551,8 +1556,11 @@
         <v>28</v>
       </c>
       <c r="W2" s="2"/>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -1603,8 +1611,11 @@
         <v>28</v>
       </c>
       <c r="W3" s="2"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -1655,8 +1666,11 @@
         <v>28</v>
       </c>
       <c r="W4" s="2"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -1707,8 +1721,11 @@
         <v>28</v>
       </c>
       <c r="W5" s="2"/>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -1759,8 +1776,11 @@
         <v>28</v>
       </c>
       <c r="W6" s="2"/>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -1811,8 +1831,11 @@
         <v>28</v>
       </c>
       <c r="W7" s="2"/>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -1863,8 +1886,11 @@
         <v>28</v>
       </c>
       <c r="W8" s="2"/>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -1915,8 +1941,11 @@
         <v>28</v>
       </c>
       <c r="W9" s="2"/>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -1967,8 +1996,11 @@
         <v>28</v>
       </c>
       <c r="W10" s="2"/>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -2019,8 +2051,11 @@
         <v>28</v>
       </c>
       <c r="W11" s="2"/>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -2071,8 +2106,11 @@
         <v>28</v>
       </c>
       <c r="W12" s="2"/>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -2123,8 +2161,11 @@
         <v>28</v>
       </c>
       <c r="W13" s="2"/>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -2175,8 +2216,11 @@
         <v>28</v>
       </c>
       <c r="W14" s="2"/>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -2227,8 +2271,11 @@
         <v>28</v>
       </c>
       <c r="W15" s="2"/>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -2279,8 +2326,11 @@
         <v>28</v>
       </c>
       <c r="W16" s="2"/>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -2331,8 +2381,11 @@
         <v>28</v>
       </c>
       <c r="W17" s="2"/>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -2383,8 +2436,11 @@
         <v>28</v>
       </c>
       <c r="W18" s="2"/>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -2435,8 +2491,11 @@
         <v>28</v>
       </c>
       <c r="W19" s="2"/>
-    </row>
-    <row r="20" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X19" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="20" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -2487,8 +2546,11 @@
         <v>28</v>
       </c>
       <c r="W20" s="2"/>
-    </row>
-    <row r="21" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X20" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="21" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -2539,8 +2601,11 @@
         <v>28</v>
       </c>
       <c r="W21" s="2"/>
-    </row>
-    <row r="22" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X21" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="22" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -2591,8 +2656,11 @@
         <v>28</v>
       </c>
       <c r="W22" s="2"/>
-    </row>
-    <row r="23" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X22" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="23" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -2642,8 +2710,11 @@
         <v>28</v>
       </c>
       <c r="W23" s="2"/>
-    </row>
-    <row r="24" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X23" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="24" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -2694,8 +2765,11 @@
         <v>28</v>
       </c>
       <c r="W24" s="2"/>
-    </row>
-    <row r="25" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X24" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="25" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -2746,8 +2820,11 @@
         <v>28</v>
       </c>
       <c r="W25" s="2"/>
-    </row>
-    <row r="26" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X25" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -2798,8 +2875,11 @@
         <v>28</v>
       </c>
       <c r="W26" s="2"/>
-    </row>
-    <row r="27" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X26" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="27" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -2850,8 +2930,11 @@
         <v>28</v>
       </c>
       <c r="W27" s="2"/>
-    </row>
-    <row r="28" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X27" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="28" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -2902,8 +2985,11 @@
         <v>28</v>
       </c>
       <c r="W28" s="2"/>
-    </row>
-    <row r="29" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X28" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="29" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>30</v>
       </c>
@@ -2954,8 +3040,11 @@
         <v>28</v>
       </c>
       <c r="W29" s="2"/>
-    </row>
-    <row r="30" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X29" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="30" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>33</v>
       </c>
@@ -3006,8 +3095,11 @@
         <v>28</v>
       </c>
       <c r="W30" s="2"/>
-    </row>
-    <row r="31" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X30" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="31" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>34</v>
       </c>
@@ -3058,8 +3150,11 @@
         <v>28</v>
       </c>
       <c r="W31" s="2"/>
-    </row>
-    <row r="32" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X31" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="32" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>35</v>
       </c>
@@ -3110,8 +3205,11 @@
         <v>28</v>
       </c>
       <c r="W32" s="2"/>
-    </row>
-    <row r="33" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X32" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="33" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>36</v>
       </c>
@@ -3162,8 +3260,11 @@
         <v>28</v>
       </c>
       <c r="W33" s="2"/>
-    </row>
-    <row r="34" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X33" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="34" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>37</v>
       </c>
@@ -3214,8 +3315,11 @@
         <v>28</v>
       </c>
       <c r="W34" s="2"/>
-    </row>
-    <row r="35" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X34" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="35" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>38</v>
       </c>
@@ -3266,8 +3370,11 @@
         <v>28</v>
       </c>
       <c r="W35" s="2"/>
-    </row>
-    <row r="36" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X35" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="36" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>39</v>
       </c>
@@ -3318,8 +3425,11 @@
         <v>28</v>
       </c>
       <c r="W36" s="2"/>
-    </row>
-    <row r="37" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X36" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="37" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>40</v>
       </c>
@@ -3370,8 +3480,11 @@
         <v>28</v>
       </c>
       <c r="W37" s="2"/>
-    </row>
-    <row r="38" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X37" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="38" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>41</v>
       </c>
@@ -3422,8 +3535,11 @@
         <v>28</v>
       </c>
       <c r="W38" s="2"/>
-    </row>
-    <row r="39" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X38" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="39" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>43</v>
       </c>
@@ -3474,8 +3590,11 @@
         <v>28</v>
       </c>
       <c r="W39" s="2"/>
-    </row>
-    <row r="40" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X39" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="40" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>44</v>
       </c>
@@ -3526,8 +3645,11 @@
         <v>28</v>
       </c>
       <c r="W40" s="2"/>
-    </row>
-    <row r="41" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X40" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="41" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>45</v>
       </c>
@@ -3578,8 +3700,11 @@
         <v>28</v>
       </c>
       <c r="W41" s="2"/>
-    </row>
-    <row r="42" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X41" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="42" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>46</v>
       </c>
@@ -3630,8 +3755,11 @@
         <v>28</v>
       </c>
       <c r="W42" s="2"/>
-    </row>
-    <row r="43" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X42" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="43" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>47</v>
       </c>
@@ -3682,8 +3810,11 @@
         <v>28</v>
       </c>
       <c r="W43" s="2"/>
-    </row>
-    <row r="44" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X43" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="44" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>48</v>
       </c>
@@ -3734,8 +3865,11 @@
         <v>28</v>
       </c>
       <c r="W44" s="2"/>
-    </row>
-    <row r="45" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X44" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="45" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>50</v>
       </c>
@@ -3786,8 +3920,11 @@
         <v>28</v>
       </c>
       <c r="W45" s="2"/>
-    </row>
-    <row r="46" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X45" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="46" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>52</v>
       </c>
@@ -3838,8 +3975,11 @@
         <v>28</v>
       </c>
       <c r="W46" s="2"/>
-    </row>
-    <row r="47" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X46" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="47" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>53</v>
       </c>
@@ -3890,8 +4030,11 @@
         <v>28</v>
       </c>
       <c r="W47" s="2"/>
-    </row>
-    <row r="48" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X47" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="48" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>54</v>
       </c>
@@ -3942,8 +4085,11 @@
         <v>28</v>
       </c>
       <c r="W48" s="2"/>
-    </row>
-    <row r="49" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X48" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="49" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>55</v>
       </c>
@@ -3994,8 +4140,11 @@
         <v>28</v>
       </c>
       <c r="W49" s="2"/>
-    </row>
-    <row r="50" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X49" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="50" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>56</v>
       </c>
@@ -4046,8 +4195,11 @@
         <v>28</v>
       </c>
       <c r="W50" s="2"/>
-    </row>
-    <row r="51" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X50" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="51" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>57</v>
       </c>
@@ -4098,8 +4250,11 @@
         <v>28</v>
       </c>
       <c r="W51" s="2"/>
-    </row>
-    <row r="52" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X51" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="52" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>58</v>
       </c>
@@ -4150,8 +4305,11 @@
         <v>28</v>
       </c>
       <c r="W52" s="2"/>
-    </row>
-    <row r="53" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X52" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="53" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>59</v>
       </c>
@@ -4202,8 +4360,11 @@
         <v>28</v>
       </c>
       <c r="W53" s="2"/>
-    </row>
-    <row r="54" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X53" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="54" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>60</v>
       </c>
@@ -4254,8 +4415,11 @@
         <v>28</v>
       </c>
       <c r="W54" s="2"/>
-    </row>
-    <row r="55" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X54" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="55" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>61</v>
       </c>
@@ -4306,8 +4470,11 @@
         <v>28</v>
       </c>
       <c r="W55" s="2"/>
-    </row>
-    <row r="56" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X55" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="56" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>62</v>
       </c>
@@ -4358,8 +4525,11 @@
         <v>28</v>
       </c>
       <c r="W56" s="2"/>
-    </row>
-    <row r="57" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X56" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="57" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>63</v>
       </c>
@@ -4410,8 +4580,11 @@
         <v>28</v>
       </c>
       <c r="W57" s="2"/>
-    </row>
-    <row r="58" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X57" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="58" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>64</v>
       </c>
@@ -4462,8 +4635,11 @@
         <v>28</v>
       </c>
       <c r="W58" s="2"/>
-    </row>
-    <row r="59" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X58" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="59" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>65</v>
       </c>
@@ -4514,8 +4690,11 @@
         <v>28</v>
       </c>
       <c r="W59" s="2"/>
-    </row>
-    <row r="60" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X59" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="60" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>66</v>
       </c>
@@ -4566,8 +4745,11 @@
         <v>28</v>
       </c>
       <c r="W60" s="2"/>
-    </row>
-    <row r="61" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X60" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="61" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>67</v>
       </c>
@@ -4618,8 +4800,11 @@
         <v>28</v>
       </c>
       <c r="W61" s="2"/>
-    </row>
-    <row r="62" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X61" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="62" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>68</v>
       </c>
@@ -4670,8 +4855,11 @@
         <v>28</v>
       </c>
       <c r="W62" s="2"/>
-    </row>
-    <row r="63" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X62" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="63" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>69</v>
       </c>
@@ -4723,8 +4911,11 @@
         <v>28</v>
       </c>
       <c r="W63" s="7"/>
-    </row>
-    <row r="64" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X63" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="64" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>70</v>
       </c>
@@ -4776,8 +4967,11 @@
         <v>28</v>
       </c>
       <c r="W64" s="7"/>
-    </row>
-    <row r="65" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X64" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="65" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>71</v>
       </c>
@@ -4828,8 +5022,11 @@
         <v>28</v>
       </c>
       <c r="W65" s="7"/>
-    </row>
-    <row r="66" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X65" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="66" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>72</v>
       </c>
@@ -4880,8 +5077,11 @@
         <v>28</v>
       </c>
       <c r="W66" s="7"/>
-    </row>
-    <row r="67" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X66" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="67" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>73</v>
       </c>
@@ -4932,8 +5132,11 @@
         <v>28</v>
       </c>
       <c r="W67" s="7"/>
-    </row>
-    <row r="68" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X67" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="68" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A68">
         <v>74</v>
       </c>
@@ -4984,8 +5187,11 @@
         <v>28</v>
       </c>
       <c r="W68" s="7"/>
-    </row>
-    <row r="69" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X68" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="69" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A69">
         <v>77</v>
       </c>
@@ -5036,8 +5242,11 @@
         <v>28</v>
       </c>
       <c r="W69" s="7"/>
-    </row>
-    <row r="70" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X69" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="70" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A70">
         <v>78</v>
       </c>
@@ -5088,8 +5297,11 @@
         <v>28</v>
       </c>
       <c r="W70" s="7"/>
-    </row>
-    <row r="71" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X70" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="71" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A71">
         <v>79</v>
       </c>
@@ -5140,8 +5352,11 @@
         <v>28</v>
       </c>
       <c r="W71" s="7"/>
-    </row>
-    <row r="72" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X71" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="72" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A72">
         <v>80</v>
       </c>
@@ -5192,8 +5407,11 @@
         <v>28</v>
       </c>
       <c r="W72" s="7"/>
-    </row>
-    <row r="73" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X72" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="73" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A73">
         <v>81</v>
       </c>
@@ -5244,8 +5462,11 @@
         <v>28</v>
       </c>
       <c r="W73" s="7"/>
-    </row>
-    <row r="74" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X73" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="74" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A74">
         <v>82</v>
       </c>
@@ -5296,8 +5517,11 @@
         <v>28</v>
       </c>
       <c r="W74" s="7"/>
-    </row>
-    <row r="75" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X74" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="75" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A75">
         <v>83</v>
       </c>
@@ -5348,8 +5572,11 @@
         <v>28</v>
       </c>
       <c r="W75" s="7"/>
-    </row>
-    <row r="76" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X75" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="76" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A76">
         <v>84</v>
       </c>
@@ -5400,8 +5627,11 @@
         <v>28</v>
       </c>
       <c r="W76" s="7"/>
-    </row>
-    <row r="77" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X76" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="77" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A77">
         <v>85</v>
       </c>
@@ -5438,8 +5668,11 @@
         <v>28</v>
       </c>
       <c r="W77" s="7"/>
-    </row>
-    <row r="78" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X77" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="78" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A78">
         <v>86</v>
       </c>
@@ -5482,8 +5715,11 @@
       <c r="V78" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="79" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X78" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="79" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A79">
         <v>87</v>
       </c>
@@ -5526,8 +5762,11 @@
       <c r="V79" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="80" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X79" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="80" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A80">
         <v>88</v>
       </c>
@@ -5570,8 +5809,11 @@
       <c r="V80" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="81" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X80" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="81" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A81">
         <v>89</v>
       </c>
@@ -5614,8 +5856,11 @@
       <c r="V81" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="82" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X81" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="82" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A82">
         <v>90</v>
       </c>
@@ -5658,8 +5903,11 @@
       <c r="V82" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="83" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X82" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="83" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A83">
         <v>91</v>
       </c>
@@ -5702,8 +5950,11 @@
       <c r="V83" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="84" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X83" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="84" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A84">
         <v>92</v>
       </c>
@@ -5746,8 +5997,11 @@
       <c r="V84" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="85" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X84" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="85" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A85">
         <v>93</v>
       </c>
@@ -5790,8 +6044,11 @@
       <c r="V85" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="86" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X85" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="86" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A86">
         <v>94</v>
       </c>
@@ -5834,8 +6091,11 @@
       <c r="V86" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="87" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X86" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="87" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A87">
         <v>95</v>
       </c>
@@ -5878,8 +6138,11 @@
       <c r="V87" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="88" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X87" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="88" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A88">
         <v>96</v>
       </c>
@@ -5922,8 +6185,11 @@
       <c r="V88" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="89" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X88" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="89" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A89">
         <v>97</v>
       </c>
@@ -5966,8 +6232,11 @@
       <c r="V89" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="90" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X89" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="90" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A90">
         <v>98</v>
       </c>
@@ -6010,8 +6279,11 @@
       <c r="V90" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="91" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X90" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="91" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A91">
         <v>99</v>
       </c>
@@ -6054,8 +6326,11 @@
       <c r="V91" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="92" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X91" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="92" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A92">
         <v>100</v>
       </c>
@@ -6098,8 +6373,11 @@
       <c r="V92" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="93" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X92" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="93" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A93">
         <v>101</v>
       </c>
@@ -6142,8 +6420,11 @@
       <c r="V93" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="94" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X93" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="94" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A94">
         <v>102</v>
       </c>
@@ -6186,8 +6467,11 @@
       <c r="V94" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="95" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X94" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="95" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A95">
         <v>103</v>
       </c>
@@ -6230,8 +6514,11 @@
       <c r="V95" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="96" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X95" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="96" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A96">
         <v>104</v>
       </c>
@@ -6274,8 +6561,11 @@
       <c r="V96" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="97" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X96" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="97" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A97">
         <v>105</v>
       </c>
@@ -6318,8 +6608,11 @@
       <c r="V97" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="98" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X97" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="98" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A98">
         <v>106</v>
       </c>
@@ -6362,8 +6655,11 @@
       <c r="V98" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="99" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X98" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="99" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A99">
         <v>107</v>
       </c>
@@ -6406,8 +6702,11 @@
       <c r="V99" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="100" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X99" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="100" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A100">
         <v>108</v>
       </c>
@@ -6450,8 +6749,11 @@
       <c r="V100" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="101" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X100" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="101" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A101">
         <v>109</v>
       </c>
@@ -6494,8 +6796,11 @@
       <c r="V101" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="102" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X101" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="102" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A102">
         <v>110</v>
       </c>
@@ -6538,8 +6843,11 @@
       <c r="V102" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="103" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X102" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="103" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A103">
         <v>116</v>
       </c>
@@ -6579,8 +6887,11 @@
       <c r="V103" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="104" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X103" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="104" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A104">
         <v>117</v>
       </c>
@@ -6623,8 +6934,11 @@
       <c r="V104" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="105" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X104" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="105" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A105">
         <v>118</v>
       </c>
@@ -6667,8 +6981,11 @@
       <c r="V105" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="106" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X105" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="106" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A106">
         <v>119</v>
       </c>
@@ -6711,8 +7028,11 @@
       <c r="V106" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="107" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X106" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="107" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A107">
         <v>120</v>
       </c>
@@ -6755,8 +7075,11 @@
       <c r="V107" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="108" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X107" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="108" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A108">
         <v>121</v>
       </c>
@@ -6799,8 +7122,11 @@
       <c r="V108" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="109" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X108" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="109" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A109">
         <v>122</v>
       </c>
@@ -6843,8 +7169,11 @@
       <c r="V109" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="110" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X109" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="110" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A110">
         <v>123</v>
       </c>
@@ -6887,8 +7216,11 @@
       <c r="V110" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="111" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X110" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="111" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A111">
         <v>124</v>
       </c>
@@ -6931,8 +7263,11 @@
       <c r="V111" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="112" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X111" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="112" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A112">
         <v>125</v>
       </c>
@@ -6975,8 +7310,11 @@
       <c r="V112" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="113" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X112" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="113" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A113">
         <v>126</v>
       </c>
@@ -7019,8 +7357,11 @@
       <c r="V113" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="114" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X113" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="114" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A114">
         <v>127</v>
       </c>
@@ -7063,8 +7404,11 @@
       <c r="V114" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="115" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X114" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="115" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A115">
         <v>128</v>
       </c>
@@ -7107,8 +7451,11 @@
       <c r="V115" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="116" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X115" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="116" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A116">
         <v>129</v>
       </c>
@@ -7151,8 +7498,11 @@
       <c r="V116" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="117" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X116" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="117" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A117">
         <v>130</v>
       </c>
@@ -7195,8 +7545,11 @@
       <c r="V117" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="118" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X117" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="118" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A118">
         <v>131</v>
       </c>
@@ -7239,8 +7592,11 @@
       <c r="V118" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="119" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X118" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="119" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A119">
         <v>132</v>
       </c>
@@ -7283,8 +7639,11 @@
       <c r="V119" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="120" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X119" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="120" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A120">
         <v>133</v>
       </c>
@@ -7327,8 +7686,11 @@
       <c r="V120" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="121" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X120" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="121" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A121">
         <v>134</v>
       </c>
@@ -7371,8 +7733,11 @@
       <c r="V121" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="122" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X121" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="122" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A122">
         <v>135</v>
       </c>
@@ -7415,8 +7780,11 @@
       <c r="V122" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="123" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X122" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="123" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A123">
         <v>136</v>
       </c>
@@ -7459,8 +7827,11 @@
       <c r="V123" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="124" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X123" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="124" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A124">
         <v>137</v>
       </c>
@@ -7503,8 +7874,11 @@
       <c r="V124" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="125" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X124" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="125" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A125">
         <v>138</v>
       </c>
@@ -7547,8 +7921,11 @@
       <c r="V125" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="126" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X125" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="126" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A126">
         <v>139</v>
       </c>
@@ -7591,8 +7968,11 @@
       <c r="V126" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="127" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X126" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="127" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A127">
         <v>140</v>
       </c>
@@ -7635,8 +8015,11 @@
       <c r="V127" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="128" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X127" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="128" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A128">
         <v>141</v>
       </c>
@@ -7679,8 +8062,11 @@
       <c r="V128" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="129" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X128" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="129" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A129">
         <v>142</v>
       </c>
@@ -7723,8 +8109,11 @@
       <c r="V129" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="130" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X129" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="130" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A130">
         <v>143</v>
       </c>
@@ -7767,8 +8156,11 @@
       <c r="V130" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="131" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X130" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="131" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A131">
         <v>144</v>
       </c>
@@ -7811,8 +8203,11 @@
       <c r="V131" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="132" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X131" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="132" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A132">
         <v>145</v>
       </c>
@@ -7855,8 +8250,11 @@
       <c r="V132" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="133" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X132" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="133" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A133">
         <v>146</v>
       </c>
@@ -7899,8 +8297,11 @@
       <c r="V133" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="134" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X133" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="134" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A134">
         <v>147</v>
       </c>
@@ -7943,8 +8344,11 @@
       <c r="V134" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="135" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X134" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="135" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A135">
         <v>148</v>
       </c>
@@ -7987,8 +8391,11 @@
       <c r="V135" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="136" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X135" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="136" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A136">
         <v>149</v>
       </c>
@@ -8031,8 +8438,11 @@
       <c r="V136" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="137" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X136" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="137" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A137">
         <v>150</v>
       </c>
@@ -8075,8 +8485,11 @@
       <c r="V137" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="138" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X137" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="138" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A138">
         <v>151</v>
       </c>
@@ -8119,8 +8532,11 @@
       <c r="V138" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="139" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X138" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="139" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A139">
         <v>152</v>
       </c>
@@ -8160,8 +8576,11 @@
       <c r="V139" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="140" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X139" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="140" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A140">
         <v>153</v>
       </c>
@@ -8204,8 +8623,11 @@
       <c r="V140" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="141" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X140" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="141" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A141">
         <v>154</v>
       </c>
@@ -8248,8 +8670,11 @@
       <c r="V141" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="142" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X141" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="142" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A142">
         <v>155</v>
       </c>
@@ -8292,8 +8717,11 @@
       <c r="V142" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="143" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X142" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="143" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A143">
         <v>156</v>
       </c>
@@ -8336,8 +8764,11 @@
       <c r="V143" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="144" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X143" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="144" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A144">
         <v>157</v>
       </c>
@@ -8380,8 +8811,11 @@
       <c r="V144" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="145" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X144" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="145" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A145">
         <v>158</v>
       </c>
@@ -8424,8 +8858,11 @@
       <c r="V145" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="146" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X145" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="146" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A146">
         <v>159</v>
       </c>
@@ -8468,8 +8905,11 @@
       <c r="V146" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="147" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X146" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="147" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A147">
         <v>160</v>
       </c>
@@ -8512,8 +8952,11 @@
       <c r="V147" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="148" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X147" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="148" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A148">
         <v>161</v>
       </c>
@@ -8556,8 +8999,11 @@
       <c r="V148" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="149" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X148" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="149" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A149">
         <v>162</v>
       </c>
@@ -8600,8 +9046,11 @@
       <c r="V149" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="150" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X149" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="150" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A150">
         <v>163</v>
       </c>
@@ -8644,8 +9093,11 @@
       <c r="V150" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="151" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X150" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="151" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A151">
         <v>164</v>
       </c>
@@ -8688,8 +9140,11 @@
       <c r="V151" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="152" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X151" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="152" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A152">
         <v>165</v>
       </c>
@@ -8732,8 +9187,11 @@
       <c r="V152" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="153" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X152" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="153" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A153">
         <v>166</v>
       </c>
@@ -8776,8 +9234,11 @@
       <c r="V153" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="154" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X153" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="154" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A154">
         <v>167</v>
       </c>
@@ -8820,8 +9281,11 @@
       <c r="V154" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="155" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X154" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="155" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A155">
         <v>168</v>
       </c>
@@ -8864,8 +9328,11 @@
       <c r="V155" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="156" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X155" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="156" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A156">
         <v>169</v>
       </c>
@@ -8908,8 +9375,11 @@
       <c r="V156" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="157" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X156" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="157" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A157">
         <v>170</v>
       </c>
@@ -8952,8 +9422,11 @@
       <c r="V157" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="158" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X157" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="158" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A158">
         <v>171</v>
       </c>
@@ -8996,8 +9469,11 @@
       <c r="V158" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="159" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X158" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="159" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A159">
         <v>172</v>
       </c>
@@ -9040,8 +9516,11 @@
       <c r="V159" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="160" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X159" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="160" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A160">
         <v>175</v>
       </c>
@@ -9084,8 +9563,11 @@
       <c r="V160" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="161" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X160" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="161" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A161">
         <v>176</v>
       </c>
@@ -9128,8 +9610,11 @@
       <c r="V161" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="162" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X161" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="162" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A162">
         <v>177</v>
       </c>
@@ -9172,8 +9657,11 @@
       <c r="V162" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="163" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X162" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="163" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A163">
         <v>178</v>
       </c>
@@ -9216,8 +9704,11 @@
       <c r="V163" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="164" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X163" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="164" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A164">
         <v>179</v>
       </c>
@@ -9260,8 +9751,11 @@
       <c r="V164" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="165" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X164" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="165" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A165">
         <v>180</v>
       </c>
@@ -9304,8 +9798,11 @@
       <c r="V165" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="166" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X165" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="166" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A166">
         <v>181</v>
       </c>
@@ -9348,8 +9845,11 @@
       <c r="V166" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="167" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X166" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="167" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A167">
         <v>182</v>
       </c>
@@ -9392,8 +9892,11 @@
       <c r="V167" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="168" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X167" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="168" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A168">
         <v>183</v>
       </c>
@@ -9436,8 +9939,11 @@
       <c r="V168" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="169" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X168" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="169" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A169">
         <v>184</v>
       </c>
@@ -9480,8 +9986,11 @@
       <c r="V169" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="170" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X169" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="170" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A170">
         <v>185</v>
       </c>
@@ -9524,8 +10033,11 @@
       <c r="V170" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="171" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X170" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="171" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A171">
         <v>186</v>
       </c>
@@ -9568,8 +10080,11 @@
       <c r="V171" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="172" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X171" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="172" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A172">
         <v>187</v>
       </c>
@@ -9612,8 +10127,11 @@
       <c r="V172" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="173" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X172" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="173" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A173">
         <v>188</v>
       </c>
@@ -9656,8 +10174,11 @@
       <c r="V173" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="174" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X173" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="174" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A174">
         <v>189</v>
       </c>
@@ -9700,8 +10221,11 @@
       <c r="V174" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="175" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X174" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="175" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A175">
         <v>190</v>
       </c>
@@ -9744,8 +10268,11 @@
       <c r="V175" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="176" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X175" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="176" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A176">
         <v>191</v>
       </c>
@@ -9788,8 +10315,11 @@
       <c r="V176" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="177" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X176" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="177" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A177">
         <v>192</v>
       </c>
@@ -9832,8 +10362,11 @@
       <c r="V177" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="178" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X177" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="178" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A178">
         <v>193</v>
       </c>
@@ -9876,8 +10409,11 @@
       <c r="V178" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="179" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X178" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="179" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A179">
         <v>194</v>
       </c>
@@ -9920,8 +10456,11 @@
       <c r="V179" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="180" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X179" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="180" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A180">
         <v>195</v>
       </c>
@@ -9964,8 +10503,11 @@
       <c r="V180" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="181" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X180" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="181" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A181">
         <v>196</v>
       </c>
@@ -10008,8 +10550,11 @@
       <c r="V181" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="182" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X181" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="182" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A182">
         <v>197</v>
       </c>
@@ -10052,8 +10597,11 @@
       <c r="V182" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="183" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X182" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="183" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A183">
         <v>198</v>
       </c>
@@ -10096,8 +10644,11 @@
       <c r="V183" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="184" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X183" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="184" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A184">
         <v>199</v>
       </c>
@@ -10140,8 +10691,11 @@
       <c r="V184" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="185" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X184" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="185" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A185">
         <v>200</v>
       </c>
@@ -10184,8 +10738,11 @@
       <c r="V185" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="186" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X185" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="186" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A186">
         <v>201</v>
       </c>
@@ -10228,8 +10785,11 @@
       <c r="V186" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="187" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X186" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="187" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A187">
         <v>202</v>
       </c>
@@ -10272,8 +10832,11 @@
       <c r="V187" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="188" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X187" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="188" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A188">
         <v>203</v>
       </c>
@@ -10316,8 +10879,11 @@
       <c r="V188" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="189" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X188" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="189" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A189">
         <v>204</v>
       </c>
@@ -10360,8 +10926,11 @@
       <c r="V189" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="190" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X189" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="190" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A190">
         <v>205</v>
       </c>
@@ -10404,8 +10973,11 @@
       <c r="V190" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="191" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X190" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="191" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A191">
         <v>206</v>
       </c>
@@ -10448,8 +11020,11 @@
       <c r="V191" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="192" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X191" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="192" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A192">
         <v>207</v>
       </c>
@@ -10492,8 +11067,11 @@
       <c r="V192" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="193" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X192" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="193" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A193">
         <v>208</v>
       </c>
@@ -10536,8 +11114,11 @@
       <c r="V193" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="194" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X193" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="194" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A194">
         <v>209</v>
       </c>
@@ -10580,8 +11161,11 @@
       <c r="V194" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="195" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X194" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="195" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A195">
         <v>210</v>
       </c>
@@ -10624,8 +11208,11 @@
       <c r="V195" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="196" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X195" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="196" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A196">
         <v>211</v>
       </c>
@@ -10668,8 +11255,11 @@
       <c r="V196" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="197" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X196" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="197" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A197">
         <v>212</v>
       </c>
@@ -10709,8 +11299,11 @@
       <c r="V197" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="198" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X197" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="198" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A198">
         <v>213</v>
       </c>
@@ -10753,8 +11346,11 @@
       <c r="V198" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="199" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X198" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="199" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A199">
         <v>214</v>
       </c>
@@ -10797,8 +11393,11 @@
       <c r="V199" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="200" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X199" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="200" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A200">
         <v>215</v>
       </c>
@@ -10841,8 +11440,11 @@
       <c r="V200" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="201" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X200" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="201" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A201">
         <v>216</v>
       </c>
@@ -10885,8 +11487,11 @@
       <c r="V201" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="202" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X201" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="202" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A202">
         <v>217</v>
       </c>
@@ -10929,8 +11534,11 @@
       <c r="V202" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="203" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X202" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="203" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A203">
         <v>218</v>
       </c>
@@ -10973,8 +11581,11 @@
       <c r="V203" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="204" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X203" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="204" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A204">
         <v>219</v>
       </c>
@@ -11017,8 +11628,11 @@
       <c r="V204" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="205" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X204" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="205" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A205">
         <v>220</v>
       </c>
@@ -11061,8 +11675,11 @@
       <c r="V205" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="206" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X205" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="206" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A206">
         <v>221</v>
       </c>
@@ -11105,8 +11722,11 @@
       <c r="V206" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="207" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X206" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="207" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A207">
         <v>222</v>
       </c>
@@ -11149,8 +11769,11 @@
       <c r="V207" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="208" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X207" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="208" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A208">
         <v>223</v>
       </c>
@@ -11193,8 +11816,11 @@
       <c r="V208" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="209" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X208" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="209" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A209">
         <v>224</v>
       </c>
@@ -11237,8 +11863,11 @@
       <c r="V209" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="210" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X209" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="210" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A210">
         <v>225</v>
       </c>
@@ -11281,8 +11910,11 @@
       <c r="V210" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="211" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X210" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="211" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A211">
         <v>226</v>
       </c>
@@ -11325,8 +11957,11 @@
       <c r="V211" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="212" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X211" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="212" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A212">
         <v>227</v>
       </c>
@@ -11369,8 +12004,11 @@
       <c r="V212" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="213" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X212" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="213" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A213">
         <v>228</v>
       </c>
@@ -11413,8 +12051,11 @@
       <c r="V213" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="214" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X213" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="214" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A214">
         <v>229</v>
       </c>
@@ -11457,8 +12098,11 @@
       <c r="V214" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="215" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X214" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="215" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A215">
         <v>230</v>
       </c>
@@ -11501,8 +12145,11 @@
       <c r="V215" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="216" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X215" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="216" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A216">
         <v>231</v>
       </c>
@@ -11545,8 +12192,11 @@
       <c r="V216" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="217" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X216" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="217" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A217">
         <v>232</v>
       </c>
@@ -11589,8 +12239,11 @@
       <c r="V217" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="218" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X217" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="218" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A218">
         <v>233</v>
       </c>
@@ -11633,8 +12286,11 @@
       <c r="V218" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="219" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X218" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="219" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A219">
         <v>234</v>
       </c>
@@ -11677,8 +12333,11 @@
       <c r="V219" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="220" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X219" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="220" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A220">
         <v>235</v>
       </c>
@@ -11721,8 +12380,11 @@
       <c r="V220" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="221" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X220" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="221" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A221">
         <v>236</v>
       </c>
@@ -11765,8 +12427,11 @@
       <c r="V221" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="222" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X221" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="222" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A222">
         <v>237</v>
       </c>
@@ -11809,8 +12474,11 @@
       <c r="V222" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="223" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X222" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="223" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A223">
         <v>238</v>
       </c>
@@ -11853,8 +12521,11 @@
       <c r="V223" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="224" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X223" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="224" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A224">
         <v>239</v>
       </c>
@@ -11897,8 +12568,11 @@
       <c r="V224" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="225" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X224" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="225" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A225">
         <v>240</v>
       </c>
@@ -11947,8 +12621,11 @@
       <c r="V225" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="226" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X225" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="226" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A226">
         <v>241</v>
       </c>
@@ -11994,8 +12671,11 @@
       <c r="T226" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="227" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X226" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="227" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A227">
         <v>242</v>
       </c>
@@ -12041,8 +12721,11 @@
       <c r="T227" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="228" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X227" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="228" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A228">
         <v>243</v>
       </c>
@@ -12088,8 +12771,11 @@
       <c r="T228" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="229" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X228" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="229" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A229">
         <v>244</v>
       </c>
@@ -12124,7 +12810,7 @@
         <v>40</v>
       </c>
       <c r="Q229" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R229" t="s">
         <v>89</v>
@@ -12135,8 +12821,11 @@
       <c r="T229" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="230" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X229" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="230" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A230">
         <v>245</v>
       </c>
@@ -12171,7 +12860,7 @@
         <v>40</v>
       </c>
       <c r="Q230" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R230" t="s">
         <v>89</v>
@@ -12182,8 +12871,11 @@
       <c r="T230" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="231" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X230" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="231" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A231">
         <v>246</v>
       </c>
@@ -12212,13 +12904,16 @@
         <v>27</v>
       </c>
       <c r="Q231" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R231" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="232" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X231" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="232" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A232">
         <v>248</v>
       </c>
@@ -12255,8 +12950,11 @@
       <c r="T232" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="233" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X232" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="233" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A233">
         <v>249</v>
       </c>
@@ -12293,8 +12991,11 @@
       <c r="T233" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="234" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X233" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="234" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A234">
         <v>252</v>
       </c>
@@ -12332,7 +13033,7 @@
         <v>42125</v>
       </c>
       <c r="Q234" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R234" t="s">
         <v>89</v>
@@ -12343,8 +13044,11 @@
       <c r="T234" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="235" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X234" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="235" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A235">
         <v>253</v>
       </c>
@@ -12382,7 +13086,7 @@
         <v>42125</v>
       </c>
       <c r="Q235" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R235" t="s">
         <v>89</v>
@@ -12393,8 +13097,11 @@
       <c r="T235" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="236" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X235" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="236" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A236">
         <v>254</v>
       </c>
@@ -12443,8 +13150,11 @@
       <c r="T236" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="237" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X236" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="237" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A237">
         <v>255</v>
       </c>
@@ -12493,8 +13203,11 @@
       <c r="T237" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="238" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X237" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="238" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A238">
         <v>256</v>
       </c>
@@ -12535,7 +13248,7 @@
         <v>175</v>
       </c>
       <c r="Q238" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R238" t="s">
         <v>89</v>
@@ -12543,8 +13256,11 @@
       <c r="S238" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="239" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X238" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="239" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A239">
         <v>257</v>
       </c>
@@ -12585,7 +13301,7 @@
         <v>175</v>
       </c>
       <c r="Q239" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R239" t="s">
         <v>89</v>
@@ -12593,8 +13309,11 @@
       <c r="S239" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="240" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X239" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="240" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A240">
         <v>258</v>
       </c>
@@ -12635,7 +13354,7 @@
         <v>175</v>
       </c>
       <c r="Q240" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R240" t="s">
         <v>89</v>
@@ -12643,8 +13362,11 @@
       <c r="S240" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="241" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X240" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="241" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A241">
         <v>259</v>
       </c>
@@ -12685,7 +13407,7 @@
         <v>175</v>
       </c>
       <c r="Q241" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R241" t="s">
         <v>89</v>
@@ -12693,8 +13415,11 @@
       <c r="S241" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="242" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X241" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="242" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A242">
         <v>260</v>
       </c>
@@ -12740,8 +13465,11 @@
       <c r="S242" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="243" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X242" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="243" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A243">
         <v>262</v>
       </c>
@@ -12782,7 +13510,7 @@
         <v>179</v>
       </c>
       <c r="Q243" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R243" t="s">
         <v>89</v>
@@ -12793,8 +13521,11 @@
       <c r="T243" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="244" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X243" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="244" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A244">
         <v>263</v>
       </c>
@@ -12835,7 +13566,7 @@
         <v>179</v>
       </c>
       <c r="Q244" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R244" t="s">
         <v>89</v>
@@ -12846,8 +13577,11 @@
       <c r="T244" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="245" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X244" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="245" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A245">
         <v>264</v>
       </c>
@@ -12888,7 +13622,7 @@
         <v>179</v>
       </c>
       <c r="Q245" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R245" t="s">
         <v>89</v>
@@ -12899,8 +13633,11 @@
       <c r="T245" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="246" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X245" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="246" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A246">
         <v>265</v>
       </c>
@@ -12941,7 +13678,7 @@
         <v>179</v>
       </c>
       <c r="Q246" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R246" t="s">
         <v>89</v>
@@ -12952,8 +13689,11 @@
       <c r="T246" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="247" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X246" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="247" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A247">
         <v>266</v>
       </c>
@@ -12994,7 +13734,7 @@
         <v>179</v>
       </c>
       <c r="Q247" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R247" t="s">
         <v>89</v>
@@ -13005,8 +13745,11 @@
       <c r="T247" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="248" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X247" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="248" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A248">
         <v>267</v>
       </c>
@@ -13047,7 +13790,7 @@
         <v>179</v>
       </c>
       <c r="Q248" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R248" t="s">
         <v>89</v>
@@ -13058,8 +13801,11 @@
       <c r="T248" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="249" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X248" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="249" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A249">
         <v>268</v>
       </c>
@@ -13100,7 +13846,7 @@
         <v>179</v>
       </c>
       <c r="Q249" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R249" t="s">
         <v>89</v>
@@ -13111,8 +13857,11 @@
       <c r="T249" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="250" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X249" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="250" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A250">
         <v>269</v>
       </c>
@@ -13153,7 +13902,7 @@
         <v>179</v>
       </c>
       <c r="Q250" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R250" t="s">
         <v>89</v>
@@ -13164,8 +13913,11 @@
       <c r="T250" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="251" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X250" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="251" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A251">
         <v>270</v>
       </c>
@@ -13206,7 +13958,7 @@
         <v>179</v>
       </c>
       <c r="Q251" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R251" t="s">
         <v>89</v>
@@ -13217,8 +13969,11 @@
       <c r="T251" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="252" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X251" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="252" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A252">
         <v>271</v>
       </c>
@@ -13259,7 +14014,7 @@
         <v>179</v>
       </c>
       <c r="Q252" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R252" t="s">
         <v>89</v>
@@ -13270,8 +14025,11 @@
       <c r="T252" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="253" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X252" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="253" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A253">
         <v>272</v>
       </c>
@@ -13312,7 +14070,7 @@
         <v>179</v>
       </c>
       <c r="Q253" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R253" t="s">
         <v>89</v>
@@ -13323,8 +14081,11 @@
       <c r="T253" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="254" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X253" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="254" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A254">
         <v>273</v>
       </c>
@@ -13365,7 +14126,7 @@
         <v>179</v>
       </c>
       <c r="Q254" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R254" t="s">
         <v>89</v>
@@ -13376,8 +14137,11 @@
       <c r="T254" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="255" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X254" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="255" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A255">
         <v>274</v>
       </c>
@@ -13418,7 +14182,7 @@
         <v>175</v>
       </c>
       <c r="Q255" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R255" t="s">
         <v>89</v>
@@ -13429,8 +14193,11 @@
       <c r="T255" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="256" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X255" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="256" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A256">
         <v>275</v>
       </c>
@@ -13471,7 +14238,7 @@
         <v>175</v>
       </c>
       <c r="Q256" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R256" t="s">
         <v>89</v>
@@ -13482,8 +14249,11 @@
       <c r="T256" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="257" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X256" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="257" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A257">
         <v>276</v>
       </c>
@@ -13524,7 +14294,7 @@
         <v>175</v>
       </c>
       <c r="Q257" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R257" t="s">
         <v>89</v>
@@ -13535,8 +14305,11 @@
       <c r="T257" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="258" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X257" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="258" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A258">
         <v>277</v>
       </c>
@@ -13577,7 +14350,7 @@
         <v>175</v>
       </c>
       <c r="Q258" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R258" t="s">
         <v>89</v>
@@ -13588,8 +14361,11 @@
       <c r="T258" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="259" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X258" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="259" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A259">
         <v>279</v>
       </c>
@@ -13630,7 +14406,7 @@
         <v>175</v>
       </c>
       <c r="Q259" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R259" t="s">
         <v>89</v>
@@ -13641,8 +14417,11 @@
       <c r="T259" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="260" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X259" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="260" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A260">
         <v>280</v>
       </c>
@@ -13683,7 +14462,7 @@
         <v>175</v>
       </c>
       <c r="Q260" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R260" t="s">
         <v>89</v>
@@ -13694,8 +14473,11 @@
       <c r="T260" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="261" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X260" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="261" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A261">
         <v>281</v>
       </c>
@@ -13747,8 +14529,11 @@
       <c r="T261" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="262" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X261" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="262" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A262">
         <v>282</v>
       </c>
@@ -13800,8 +14585,11 @@
       <c r="T262" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="263" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X262" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="263" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A263">
         <v>283</v>
       </c>
@@ -13842,7 +14630,7 @@
         <v>175</v>
       </c>
       <c r="Q263" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R263" t="s">
         <v>89</v>
@@ -13853,8 +14641,11 @@
       <c r="T263" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="264" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X263" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="264" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A264">
         <v>284</v>
       </c>
@@ -13895,7 +14686,7 @@
         <v>175</v>
       </c>
       <c r="Q264" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R264" t="s">
         <v>89</v>
@@ -13903,8 +14694,11 @@
       <c r="S264" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="265" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X264" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="265" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A265">
         <v>286</v>
       </c>
@@ -13945,7 +14739,7 @@
         <v>175</v>
       </c>
       <c r="Q265" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R265" t="s">
         <v>89</v>
@@ -13956,8 +14750,11 @@
       <c r="T265" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="266" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X265" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="266" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A266">
         <v>287</v>
       </c>
@@ -13998,7 +14795,7 @@
         <v>196</v>
       </c>
       <c r="Q266" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R266" t="s">
         <v>89</v>
@@ -14006,8 +14803,11 @@
       <c r="S266" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="267" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X266" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="267" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A267">
         <v>293</v>
       </c>
@@ -14059,8 +14859,11 @@
       <c r="T267" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="268" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X267" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="268" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A268">
         <v>294</v>
       </c>
@@ -14112,8 +14915,11 @@
       <c r="T268" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="269" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X268" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="269" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A269">
         <v>295</v>
       </c>
@@ -14165,8 +14971,11 @@
       <c r="T269" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="270" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X269" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="270" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A270">
         <v>296</v>
       </c>
@@ -14218,8 +15027,11 @@
       <c r="T270" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="271" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X270" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="271" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A271">
         <v>297</v>
       </c>
@@ -14262,8 +15074,11 @@
       <c r="S271" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="272" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X271" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="272" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A272">
         <v>298</v>
       </c>
@@ -14312,8 +15127,11 @@
       <c r="T272" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="273" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X272" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="273" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A273">
         <v>299</v>
       </c>
@@ -14362,8 +15180,11 @@
       <c r="T273" t="s">
         <v>200</v>
       </c>
-    </row>
-    <row r="274" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X273" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="274" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A274">
         <v>301</v>
       </c>
@@ -14412,8 +15233,11 @@
       <c r="S274" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="275" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X274" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="275" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A275">
         <v>302</v>
       </c>
@@ -14462,8 +15286,11 @@
       <c r="T275" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="276" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X275" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="276" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A276">
         <v>303</v>
       </c>
@@ -14512,8 +15339,11 @@
       <c r="T276" t="s">
         <v>201</v>
       </c>
-    </row>
-    <row r="277" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X276" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="277" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A277">
         <v>304</v>
       </c>
@@ -14565,8 +15395,11 @@
       <c r="T277" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="278" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X277" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="278" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A278">
         <v>305</v>
       </c>
@@ -14615,8 +15448,11 @@
       <c r="T278" t="s">
         <v>203</v>
       </c>
-    </row>
-    <row r="279" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X278" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="279" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A279">
         <v>306</v>
       </c>
@@ -14657,7 +15493,7 @@
         <v>175</v>
       </c>
       <c r="Q279" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R279" t="s">
         <v>89</v>
@@ -14668,8 +15504,11 @@
       <c r="T279" t="s">
         <v>205</v>
       </c>
-    </row>
-    <row r="280" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X279" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="280" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A280">
         <v>307</v>
       </c>
@@ -14721,8 +15560,11 @@
       <c r="T280" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="281" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X280" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="281" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A281">
         <v>308</v>
       </c>
@@ -14774,8 +15616,11 @@
       <c r="T281" t="s">
         <v>207</v>
       </c>
-    </row>
-    <row r="282" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X281" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="282" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A282">
         <v>312</v>
       </c>
@@ -14827,8 +15672,11 @@
       <c r="T282" t="s">
         <v>208</v>
       </c>
-    </row>
-    <row r="283" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X282" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="283" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A283">
         <v>313</v>
       </c>
@@ -14880,8 +15728,11 @@
       <c r="T283" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="284" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X283" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="284" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A284">
         <v>314</v>
       </c>
@@ -14933,8 +15784,11 @@
       <c r="T284" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="285" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X284" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="285" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A285">
         <v>315</v>
       </c>
@@ -14986,8 +15840,11 @@
       <c r="T285" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="286" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X285" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="286" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A286">
         <v>316</v>
       </c>
@@ -15039,8 +15896,11 @@
       <c r="T286" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="287" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X286" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="287" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A287">
         <v>317</v>
       </c>
@@ -15092,8 +15952,11 @@
       <c r="T287" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="288" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X287" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="288" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A288">
         <v>318</v>
       </c>
@@ -15145,8 +16008,11 @@
       <c r="T288" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="289" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X288" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="289" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A289">
         <v>319</v>
       </c>
@@ -15198,8 +16064,11 @@
       <c r="T289" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="290" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X289" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="290" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A290">
         <v>320</v>
       </c>
@@ -15251,8 +16120,11 @@
       <c r="T290" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="291" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X290" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="291" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A291">
         <v>321</v>
       </c>
@@ -15304,8 +16176,11 @@
       <c r="T291" t="s">
         <v>210</v>
       </c>
-    </row>
-    <row r="292" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X291" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="292" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A292">
         <v>322</v>
       </c>
@@ -15354,8 +16229,11 @@
       <c r="S292" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="293" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X292" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="293" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A293">
         <v>323</v>
       </c>
@@ -15407,8 +16285,11 @@
       <c r="T293" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="294" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X293" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="294" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A294">
         <v>324</v>
       </c>
@@ -15449,7 +16330,7 @@
         <v>175</v>
       </c>
       <c r="Q294" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R294" t="s">
         <v>89</v>
@@ -15460,8 +16341,11 @@
       <c r="T294" t="s">
         <v>212</v>
       </c>
-    </row>
-    <row r="295" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X294" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="295" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A295">
         <v>327</v>
       </c>
@@ -15513,8 +16397,11 @@
       <c r="T295" t="s">
         <v>209</v>
       </c>
-    </row>
-    <row r="296" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X295" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="296" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A296">
         <v>328</v>
       </c>
@@ -15566,8 +16453,11 @@
       <c r="T296" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="297" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X296" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="297" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A297">
         <v>329</v>
       </c>
@@ -15619,8 +16509,11 @@
       <c r="T297" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="298" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X297" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="298" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A298">
         <v>330</v>
       </c>
@@ -15672,8 +16565,11 @@
       <c r="T298" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="299" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X298" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="299" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A299">
         <v>331</v>
       </c>
@@ -15725,8 +16621,11 @@
       <c r="T299" t="s">
         <v>214</v>
       </c>
-    </row>
-    <row r="300" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X299" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="300" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A300">
         <v>332</v>
       </c>
@@ -15778,8 +16677,11 @@
       <c r="T300" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="301" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X300" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="301" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A301">
         <v>333</v>
       </c>
@@ -15831,8 +16733,11 @@
       <c r="T301" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="302" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X301" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="302" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A302">
         <v>334</v>
       </c>
@@ -15884,8 +16789,11 @@
       <c r="T302" t="s">
         <v>215</v>
       </c>
-    </row>
-    <row r="303" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X302" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="303" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A303">
         <v>335</v>
       </c>
@@ -15923,7 +16831,7 @@
         <v>175</v>
       </c>
       <c r="Q303" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R303" t="s">
         <v>89</v>
@@ -15934,8 +16842,11 @@
       <c r="T303" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="304" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X303" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="304" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A304">
         <v>336</v>
       </c>
@@ -15973,7 +16884,7 @@
         <v>175</v>
       </c>
       <c r="Q304" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R304" t="s">
         <v>89</v>
@@ -15984,8 +16895,11 @@
       <c r="T304" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="305" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X304" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="305" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A305">
         <v>337</v>
       </c>
@@ -16023,7 +16937,7 @@
         <v>175</v>
       </c>
       <c r="Q305" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R305" t="s">
         <v>89</v>
@@ -16034,8 +16948,11 @@
       <c r="T305" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="306" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X305" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="306" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A306">
         <v>338</v>
       </c>
@@ -16073,7 +16990,7 @@
         <v>175</v>
       </c>
       <c r="Q306" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R306" t="s">
         <v>89</v>
@@ -16084,8 +17001,11 @@
       <c r="T306" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="307" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X306" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="307" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A307">
         <v>339</v>
       </c>
@@ -16123,7 +17043,7 @@
         <v>175</v>
       </c>
       <c r="Q307" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R307" t="s">
         <v>89</v>
@@ -16134,8 +17054,11 @@
       <c r="T307" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="308" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X307" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="308" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A308">
         <v>340</v>
       </c>
@@ -16173,7 +17096,7 @@
         <v>175</v>
       </c>
       <c r="Q308" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R308" t="s">
         <v>89</v>
@@ -16184,8 +17107,11 @@
       <c r="T308" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="309" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X308" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="309" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A309">
         <v>341</v>
       </c>
@@ -16223,7 +17149,7 @@
         <v>175</v>
       </c>
       <c r="Q309" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R309" t="s">
         <v>89</v>
@@ -16234,8 +17160,11 @@
       <c r="T309" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="310" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X309" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="310" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A310">
         <v>342</v>
       </c>
@@ -16273,7 +17202,7 @@
         <v>175</v>
       </c>
       <c r="Q310" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R310" t="s">
         <v>89</v>
@@ -16284,8 +17213,11 @@
       <c r="T310" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="311" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X310" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="311" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A311">
         <v>343</v>
       </c>
@@ -16323,7 +17255,7 @@
         <v>175</v>
       </c>
       <c r="Q311" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R311" t="s">
         <v>89</v>
@@ -16334,8 +17266,11 @@
       <c r="T311" t="s">
         <v>216</v>
       </c>
-    </row>
-    <row r="312" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X311" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="312" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A312">
         <v>344</v>
       </c>
@@ -16373,7 +17308,7 @@
         <v>197</v>
       </c>
       <c r="Q312" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R312" t="s">
         <v>89</v>
@@ -16381,8 +17316,11 @@
       <c r="S312" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="313" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X312" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="313" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A313">
         <v>345</v>
       </c>
@@ -16431,8 +17369,11 @@
       <c r="S313" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="314" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X313" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="314" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A314">
         <v>346</v>
       </c>
@@ -16481,8 +17422,11 @@
       <c r="T314" t="s">
         <v>217</v>
       </c>
-    </row>
-    <row r="315" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X314" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="315" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A315">
         <v>347</v>
       </c>
@@ -16523,7 +17467,7 @@
         <v>197</v>
       </c>
       <c r="Q315" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R315" t="s">
         <v>89</v>
@@ -16534,8 +17478,11 @@
       <c r="T315" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="316" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X315" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="316" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A316">
         <v>348</v>
       </c>
@@ -16576,7 +17523,7 @@
         <v>197</v>
       </c>
       <c r="Q316" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R316" t="s">
         <v>89</v>
@@ -16587,8 +17534,11 @@
       <c r="T316" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="317" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X316" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="317" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A317">
         <v>349</v>
       </c>
@@ -16629,7 +17579,7 @@
         <v>197</v>
       </c>
       <c r="Q317" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R317" t="s">
         <v>89</v>
@@ -16640,8 +17590,11 @@
       <c r="T317" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="318" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X317" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="318" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A318">
         <v>350</v>
       </c>
@@ -16682,7 +17635,7 @@
         <v>197</v>
       </c>
       <c r="Q318" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R318" t="s">
         <v>89</v>
@@ -16693,8 +17646,11 @@
       <c r="T318" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="319" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X318" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="319" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A319">
         <v>351</v>
       </c>
@@ -16735,7 +17691,7 @@
         <v>197</v>
       </c>
       <c r="Q319" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R319" t="s">
         <v>89</v>
@@ -16746,8 +17702,11 @@
       <c r="T319" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="320" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X319" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="320" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A320">
         <v>352</v>
       </c>
@@ -16788,7 +17747,7 @@
         <v>197</v>
       </c>
       <c r="Q320" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R320" t="s">
         <v>89</v>
@@ -16799,8 +17758,11 @@
       <c r="T320" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="321" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X320" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="321" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A321">
         <v>353</v>
       </c>
@@ -16841,7 +17803,7 @@
         <v>197</v>
       </c>
       <c r="Q321" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R321" t="s">
         <v>89</v>
@@ -16852,8 +17814,11 @@
       <c r="T321" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="322" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X321" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="322" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A322">
         <v>354</v>
       </c>
@@ -16894,7 +17859,7 @@
         <v>197</v>
       </c>
       <c r="Q322" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R322" t="s">
         <v>89</v>
@@ -16905,8 +17870,11 @@
       <c r="T322" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="323" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X322" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="323" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A323">
         <v>355</v>
       </c>
@@ -16947,7 +17915,7 @@
         <v>197</v>
       </c>
       <c r="Q323" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R323" t="s">
         <v>89</v>
@@ -16958,8 +17926,11 @@
       <c r="T323" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="324" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X323" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="324" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A324">
         <v>356</v>
       </c>
@@ -17000,7 +17971,7 @@
         <v>197</v>
       </c>
       <c r="Q324" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R324" t="s">
         <v>89</v>
@@ -17011,8 +17982,11 @@
       <c r="T324" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="325" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X324" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="325" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A325">
         <v>357</v>
       </c>
@@ -17053,7 +18027,7 @@
         <v>197</v>
       </c>
       <c r="Q325" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R325" t="s">
         <v>89</v>
@@ -17064,8 +18038,11 @@
       <c r="T325" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="326" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X325" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="326" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A326">
         <v>358</v>
       </c>
@@ -17106,7 +18083,7 @@
         <v>197</v>
       </c>
       <c r="Q326" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R326" t="s">
         <v>89</v>
@@ -17117,8 +18094,11 @@
       <c r="T326" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="327" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X326" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="327" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A327">
         <v>359</v>
       </c>
@@ -17159,7 +18139,7 @@
         <v>197</v>
       </c>
       <c r="Q327" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R327" t="s">
         <v>89</v>
@@ -17170,8 +18150,11 @@
       <c r="T327" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="328" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X327" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="328" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A328">
         <v>360</v>
       </c>
@@ -17212,7 +18195,7 @@
         <v>197</v>
       </c>
       <c r="Q328" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R328" t="s">
         <v>89</v>
@@ -17223,8 +18206,11 @@
       <c r="T328" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="329" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X328" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="329" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A329">
         <v>361</v>
       </c>
@@ -17265,7 +18251,7 @@
         <v>197</v>
       </c>
       <c r="Q329" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R329" t="s">
         <v>89</v>
@@ -17276,8 +18262,11 @@
       <c r="T329" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="330" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X329" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="330" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A330">
         <v>362</v>
       </c>
@@ -17318,7 +18307,7 @@
         <v>197</v>
       </c>
       <c r="Q330" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R330" t="s">
         <v>89</v>
@@ -17329,8 +18318,11 @@
       <c r="T330" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="331" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X330" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="331" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A331">
         <v>363</v>
       </c>
@@ -17371,7 +18363,7 @@
         <v>197</v>
       </c>
       <c r="Q331" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R331" t="s">
         <v>89</v>
@@ -17382,8 +18374,11 @@
       <c r="T331" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="332" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X331" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="332" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A332">
         <v>364</v>
       </c>
@@ -17424,7 +18419,7 @@
         <v>197</v>
       </c>
       <c r="Q332" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R332" t="s">
         <v>89</v>
@@ -17435,8 +18430,11 @@
       <c r="T332" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="333" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X332" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="333" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A333">
         <v>365</v>
       </c>
@@ -17477,7 +18475,7 @@
         <v>197</v>
       </c>
       <c r="Q333" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R333" t="s">
         <v>89</v>
@@ -17488,8 +18486,11 @@
       <c r="T333" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="334" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X333" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="334" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A334">
         <v>366</v>
       </c>
@@ -17530,7 +18531,7 @@
         <v>197</v>
       </c>
       <c r="Q334" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R334" t="s">
         <v>89</v>
@@ -17541,8 +18542,11 @@
       <c r="T334" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="335" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X334" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="335" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A335">
         <v>367</v>
       </c>
@@ -17583,7 +18587,7 @@
         <v>197</v>
       </c>
       <c r="Q335" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R335" t="s">
         <v>89</v>
@@ -17594,8 +18598,11 @@
       <c r="T335" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="336" spans="1:20" x14ac:dyDescent="0.3">
+      <c r="X335" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="336" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A336">
         <v>368</v>
       </c>
@@ -17636,7 +18643,7 @@
         <v>197</v>
       </c>
       <c r="Q336" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R336" t="s">
         <v>89</v>
@@ -17647,8 +18654,11 @@
       <c r="T336" t="s">
         <v>219</v>
       </c>
-    </row>
-    <row r="337" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X336" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="337" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A337">
         <v>369</v>
       </c>
@@ -17689,7 +18699,7 @@
         <v>197</v>
       </c>
       <c r="Q337" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R337" t="s">
         <v>89</v>
@@ -17700,8 +18710,11 @@
       <c r="T337" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="338" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X337" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="338" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A338">
         <v>370</v>
       </c>
@@ -17747,8 +18760,11 @@
       <c r="T338" t="s">
         <v>221</v>
       </c>
-    </row>
-    <row r="339" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X338" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="339" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A339">
         <v>371</v>
       </c>
@@ -17800,8 +18816,11 @@
       <c r="T339" t="s">
         <v>223</v>
       </c>
-    </row>
-    <row r="340" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X339" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="340" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A340">
         <v>373</v>
       </c>
@@ -17847,8 +18866,11 @@
       <c r="T340" t="s">
         <v>224</v>
       </c>
-    </row>
-    <row r="341" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X340" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="341" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A341">
         <v>375</v>
       </c>
@@ -17889,7 +18911,7 @@
         <v>197</v>
       </c>
       <c r="Q341" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R341" t="s">
         <v>89</v>
@@ -17900,8 +18922,11 @@
       <c r="U341" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="342" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X341" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="342" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A342">
         <v>376</v>
       </c>
@@ -17942,7 +18967,7 @@
         <v>197</v>
       </c>
       <c r="Q342" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R342" t="s">
         <v>89</v>
@@ -17953,8 +18978,11 @@
       <c r="U342" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="343" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X342" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="343" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A343">
         <v>377</v>
       </c>
@@ -17995,7 +19023,7 @@
         <v>197</v>
       </c>
       <c r="Q343" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R343" t="s">
         <v>89</v>
@@ -18006,8 +19034,11 @@
       <c r="U343" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="344" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X343" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="344" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A344">
         <v>378</v>
       </c>
@@ -18048,7 +19079,7 @@
         <v>197</v>
       </c>
       <c r="Q344" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R344" t="s">
         <v>89</v>
@@ -18059,8 +19090,11 @@
       <c r="U344" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="345" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X344" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="345" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A345">
         <v>379</v>
       </c>
@@ -18101,7 +19135,7 @@
         <v>197</v>
       </c>
       <c r="Q345" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R345" t="s">
         <v>89</v>
@@ -18112,8 +19146,11 @@
       <c r="U345" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="346" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X345" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="346" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A346">
         <v>380</v>
       </c>
@@ -18154,7 +19191,7 @@
         <v>197</v>
       </c>
       <c r="Q346" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R346" t="s">
         <v>89</v>
@@ -18165,8 +19202,11 @@
       <c r="U346" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="347" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X346" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="347" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A347">
         <v>381</v>
       </c>
@@ -18207,7 +19247,7 @@
         <v>197</v>
       </c>
       <c r="Q347" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R347" t="s">
         <v>89</v>
@@ -18218,8 +19258,11 @@
       <c r="U347" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="348" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X347" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="348" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A348">
         <v>382</v>
       </c>
@@ -18260,7 +19303,7 @@
         <v>197</v>
       </c>
       <c r="Q348" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R348" t="s">
         <v>89</v>
@@ -18271,8 +19314,11 @@
       <c r="U348" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="349" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X348" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="349" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A349">
         <v>383</v>
       </c>
@@ -18303,8 +19349,11 @@
       <c r="U349" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="350" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="X349" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="350" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A350">
         <v>384</v>
       </c>
@@ -18332,10 +19381,13 @@
       <c r="R350" t="s">
         <v>89</v>
       </c>
+      <c r="X350" t="s">
+        <v>311</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:W350" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G77" xr:uid="{58155949-CB1B-48D8-A226-133575A9F708}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
     </dataValidation>
@@ -18347,6 +19399,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C77" xr:uid="{C310BEFD-AB98-4273-AFFC-E63848748976}">
       <formula1>Category</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X351" xr:uid="{79ECCAD1-C8DD-4F20-B690-FD720275E0AE}">
+      <formula1>"LandLord , B&amp;Z"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -18373,7 +19428,7 @@
     <col min="22" max="22" width="10.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:23" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -18443,8 +19498,11 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
-    </row>
-    <row r="2" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X1" s="1" t="s">
+        <v>310</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>28</v>
       </c>
@@ -18506,8 +19564,11 @@
       <c r="V2" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="3" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>29</v>
       </c>
@@ -18570,8 +19631,11 @@
         <v>28</v>
       </c>
       <c r="W3" s="7"/>
-    </row>
-    <row r="4" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>31</v>
       </c>
@@ -18634,8 +19698,11 @@
         <v>28</v>
       </c>
       <c r="W4" s="7"/>
-    </row>
-    <row r="5" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>32</v>
       </c>
@@ -18691,8 +19758,11 @@
       <c r="V5" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="6" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>42</v>
       </c>
@@ -18754,8 +19824,11 @@
       <c r="V6" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="7" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>49</v>
       </c>
@@ -18817,8 +19890,11 @@
       <c r="V7" s="2" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="8" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>51</v>
       </c>
@@ -18879,8 +19955,11 @@
       <c r="V8" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="9" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>75</v>
       </c>
@@ -18941,8 +20020,11 @@
       <c r="V9" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>76</v>
       </c>
@@ -19003,8 +20085,11 @@
       <c r="V10" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="11" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>111</v>
       </c>
@@ -19030,7 +20115,7 @@
         <v>98</v>
       </c>
       <c r="I11" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K11">
         <v>100</v>
@@ -19065,8 +20150,11 @@
       <c r="V11" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="12" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>112</v>
       </c>
@@ -19092,7 +20180,7 @@
         <v>98</v>
       </c>
       <c r="I12" t="s">
-        <v>308</v>
+        <v>307</v>
       </c>
       <c r="K12">
         <v>75</v>
@@ -19127,8 +20215,11 @@
       <c r="V12" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="13" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>113</v>
       </c>
@@ -19154,7 +20245,7 @@
         <v>98</v>
       </c>
       <c r="I13" t="s">
-        <v>307</v>
+        <v>306</v>
       </c>
       <c r="K13">
         <v>75</v>
@@ -19189,8 +20280,11 @@
       <c r="V13" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="14" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>114</v>
       </c>
@@ -19251,8 +20345,11 @@
       <c r="V14" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="15" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>173</v>
       </c>
@@ -19313,8 +20410,11 @@
       <c r="V15" t="s">
         <v>28</v>
       </c>
-    </row>
-    <row r="16" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X15" t="s">
+        <v>312</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>174</v>
       </c>
@@ -19374,6 +20474,9 @@
       </c>
       <c r="V16" t="s">
         <v>28</v>
+      </c>
+      <c r="X16" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="17" spans="1:24" x14ac:dyDescent="0.3">
@@ -19440,6 +20543,9 @@
       <c r="V17" t="s">
         <v>28</v>
       </c>
+      <c r="X17" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
@@ -19503,7 +20609,7 @@
         <v>28</v>
       </c>
       <c r="X18" t="s">
-        <v>257</v>
+        <v>311</v>
       </c>
     </row>
     <row r="19" spans="1:24" x14ac:dyDescent="0.3">
@@ -19526,7 +20632,7 @@
         <v>27</v>
       </c>
       <c r="G19" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H19" t="s">
         <v>95</v>
@@ -19566,6 +20672,9 @@
       </c>
       <c r="V19" t="s">
         <v>28</v>
+      </c>
+      <c r="X19" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="20" spans="1:24" x14ac:dyDescent="0.3">
@@ -19582,7 +20691,7 @@
         <v>55</v>
       </c>
       <c r="E20" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F20" t="s">
         <v>27</v>
@@ -19618,7 +20727,7 @@
         <v>175</v>
       </c>
       <c r="Q20" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R20" t="s">
         <v>89</v>
@@ -19627,10 +20736,13 @@
         <v>155</v>
       </c>
       <c r="T20" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
       <c r="V20" t="s">
         <v>28</v>
+      </c>
+      <c r="X20" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="21" spans="1:24" x14ac:dyDescent="0.3">
@@ -19647,7 +20759,7 @@
         <v>84</v>
       </c>
       <c r="E21" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F21" t="s">
         <v>27</v>
@@ -19665,7 +20777,7 @@
         <v>250</v>
       </c>
       <c r="L21" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M21" t="s">
         <v>27</v>
@@ -19689,10 +20801,13 @@
         <v>155</v>
       </c>
       <c r="T21" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="V21" t="s">
         <v>28</v>
+      </c>
+      <c r="X21" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="22" spans="1:24" x14ac:dyDescent="0.3">
@@ -19709,7 +20824,7 @@
         <v>84</v>
       </c>
       <c r="E22" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="F22" t="s">
         <v>27</v>
@@ -19727,7 +20842,7 @@
         <v>250</v>
       </c>
       <c r="L22" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="M22" t="s">
         <v>27</v>
@@ -19751,10 +20866,13 @@
         <v>155</v>
       </c>
       <c r="T22" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="V22" t="s">
         <v>28</v>
+      </c>
+      <c r="X22" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="23" spans="1:24" x14ac:dyDescent="0.3">
@@ -19792,7 +20910,7 @@
         <v>350</v>
       </c>
       <c r="L23" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M23" t="s">
         <v>27</v>
@@ -19816,10 +20934,13 @@
         <v>155</v>
       </c>
       <c r="T23" t="s">
-        <v>265</v>
+        <v>264</v>
       </c>
       <c r="V23" t="s">
         <v>28</v>
+      </c>
+      <c r="X23" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="24" spans="1:24" x14ac:dyDescent="0.3">
@@ -19842,7 +20963,7 @@
         <v>27</v>
       </c>
       <c r="G24" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="H24" t="s">
         <v>95</v>
@@ -19872,7 +20993,7 @@
         <v>175</v>
       </c>
       <c r="Q24" t="s">
-        <v>266</v>
+        <v>265</v>
       </c>
       <c r="R24" t="s">
         <v>89</v>
@@ -19881,10 +21002,13 @@
         <v>155</v>
       </c>
       <c r="T24" t="s">
-        <v>267</v>
+        <v>266</v>
       </c>
       <c r="V24" t="s">
         <v>28</v>
+      </c>
+      <c r="X24" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="25" spans="1:24" x14ac:dyDescent="0.3">
@@ -19898,16 +21022,16 @@
         <v>47</v>
       </c>
       <c r="D25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E25" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F25" t="s">
         <v>48</v>
       </c>
       <c r="G25" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I25" t="s">
         <v>27</v>
@@ -19919,7 +21043,7 @@
         <v>50</v>
       </c>
       <c r="L25" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M25" t="s">
         <v>27</v>
@@ -19934,7 +21058,7 @@
         <v>175</v>
       </c>
       <c r="Q25" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R25" t="s">
         <v>89</v>
@@ -19945,6 +21069,9 @@
       <c r="V25" t="s">
         <v>28</v>
       </c>
+      <c r="X25" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="26" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A26">
@@ -19957,16 +21084,16 @@
         <v>47</v>
       </c>
       <c r="D26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="E26" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="F26" t="s">
         <v>48</v>
       </c>
       <c r="G26" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="I26" t="s">
         <v>27</v>
@@ -19978,7 +21105,7 @@
         <v>50</v>
       </c>
       <c r="L26" t="s">
-        <v>264</v>
+        <v>263</v>
       </c>
       <c r="M26" t="s">
         <v>27</v>
@@ -19993,7 +21120,7 @@
         <v>175</v>
       </c>
       <c r="Q26" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="R26" t="s">
         <v>89</v>
@@ -20003,6 +21130,9 @@
       </c>
       <c r="V26" t="s">
         <v>28</v>
+      </c>
+      <c r="X26" t="s">
+        <v>312</v>
       </c>
     </row>
     <row r="27" spans="1:24" x14ac:dyDescent="0.3">
@@ -20040,7 +21170,7 @@
         <v>75</v>
       </c>
       <c r="L27" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="M27" t="s">
         <v>27</v>
@@ -20055,7 +21185,7 @@
         <v>175</v>
       </c>
       <c r="Q27" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="R27" t="s">
         <v>89</v>
@@ -20068,6 +21198,9 @@
       </c>
       <c r="V27" t="s">
         <v>28</v>
+      </c>
+      <c r="X27" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="28" spans="1:24" x14ac:dyDescent="0.3">
@@ -20105,7 +21238,7 @@
         <v>100</v>
       </c>
       <c r="L28" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="M28" t="s">
         <v>27</v>
@@ -20129,10 +21262,13 @@
         <v>155</v>
       </c>
       <c r="T28" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="V28" t="s">
         <v>28</v>
+      </c>
+      <c r="X28" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="29" spans="1:24" x14ac:dyDescent="0.3">
@@ -20146,10 +21282,10 @@
         <v>47</v>
       </c>
       <c r="D29" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="E29" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
       <c r="F29" t="s">
         <v>27</v>
@@ -20185,7 +21321,7 @@
         <v>197</v>
       </c>
       <c r="Q29" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="R29" t="s">
         <v>89</v>
@@ -20195,6 +21331,9 @@
       </c>
       <c r="V29" t="s">
         <v>28</v>
+      </c>
+      <c r="X29" t="s">
+        <v>311</v>
       </c>
     </row>
     <row r="30" spans="1:24" x14ac:dyDescent="0.3">
@@ -20258,10 +21397,13 @@
       <c r="V30" t="s">
         <v>28</v>
       </c>
+      <c r="X30" t="s">
+        <v>311</v>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:W7" xr:uid="{7AFFF102-26E2-4B46-85F9-06F0C3E86F0F}"/>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F7" xr:uid="{EFD74BD8-58C9-4ACB-93B3-5302AF9CB479}">
       <formula1>INDIRECT(D2&amp;"_material")</formula1>
     </dataValidation>
@@ -20273,6 +21415,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="C2:C7" xr:uid="{BF2AFAAE-B6D2-412A-B5FA-591E8B15DA0C}">
       <formula1>Category</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X34" xr:uid="{52827643-06B4-4CC3-A87D-0F03A7C68B25}">
+      <formula1>"LandLord , B&amp;Z"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20368,6 +21513,9 @@
       <c r="W1" t="s">
         <v>22</v>
       </c>
+      <c r="X1" s="1" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
@@ -20377,16 +21525,16 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
+        <v>275</v>
+      </c>
+      <c r="D2" t="s">
         <v>276</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>276</v>
+      </c>
+      <c r="F2" t="s">
         <v>277</v>
-      </c>
-      <c r="E2" t="s">
-        <v>277</v>
-      </c>
-      <c r="F2" t="s">
-        <v>278</v>
       </c>
       <c r="I2" t="s">
         <v>27</v>
@@ -20422,14 +21570,16 @@
         <v>155</v>
       </c>
       <c r="T2" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="U2" s="2"/>
       <c r="V2" t="s">
         <v>28</v>
       </c>
       <c r="W2" s="2"/>
-      <c r="X2" s="13"/>
+      <c r="X2" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
@@ -20439,16 +21589,16 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
+        <v>275</v>
+      </c>
+      <c r="D3" t="s">
         <v>276</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>276</v>
+      </c>
+      <c r="F3" t="s">
         <v>277</v>
-      </c>
-      <c r="E3" t="s">
-        <v>277</v>
-      </c>
-      <c r="F3" t="s">
-        <v>278</v>
       </c>
       <c r="H3" t="s">
         <v>95</v>
@@ -20487,13 +21637,16 @@
         <v>155</v>
       </c>
       <c r="T3" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="U3" s="2"/>
       <c r="V3" t="s">
         <v>28</v>
       </c>
       <c r="W3" s="2"/>
+      <c r="X3" t="s">
+        <v>311</v>
+      </c>
     </row>
     <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="E4" s="7"/>
@@ -20502,7 +21655,7 @@
       <c r="H4" s="7"/>
       <c r="I4" s="7"/>
       <c r="J4" s="7"/>
-      <c r="K4" s="14"/>
+      <c r="K4" s="13"/>
       <c r="L4" s="10"/>
       <c r="M4" s="10"/>
       <c r="N4" s="10"/>
@@ -20546,7 +21699,7 @@
       <c r="W6" s="2"/>
     </row>
   </sheetData>
-  <dataValidations count="4">
+  <dataValidations count="5">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F6" xr:uid="{049F1F64-FDBE-45B5-B292-C2C5EC3F1001}">
       <formula1>INDIRECT(D2&amp;"_material")</formula1>
     </dataValidation>
@@ -20558,6 +21711,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="G2:G6" xr:uid="{A54186C2-8BD9-4A1F-9A77-54DD56F0EC69}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X3" xr:uid="{6AD7D24E-16F4-47F5-AD0C-87B049E7E5B5}">
+      <formula1>"LandLord , B&amp;Z"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -20668,7 +21824,7 @@
     <row r="3" spans="1:27" x14ac:dyDescent="0.3">
       <c r="G3" s="11"/>
       <c r="I3" s="9"/>
-      <c r="O3" s="15"/>
+      <c r="O3" s="14"/>
       <c r="T3" s="8"/>
       <c r="X3" s="2"/>
     </row>
@@ -20702,7 +21858,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7E46FE8D-6B9D-4019-AD13-4A9515E01ECE}">
-  <dimension ref="A1:W19"/>
+  <dimension ref="A1:X19"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="3" bestFit="1" customWidth="1"/>
@@ -20715,7 +21871,7 @@
     <col min="21" max="21" width="28.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:22" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1</v>
       </c>
@@ -20779,8 +21935,11 @@
       <c r="U1" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="2" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X1" s="1" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="2" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -20788,28 +21947,28 @@
         <v>27</v>
       </c>
       <c r="C2" t="s">
+        <v>280</v>
+      </c>
+      <c r="D2" t="s">
         <v>281</v>
       </c>
-      <c r="D2" t="s">
+      <c r="E2" t="s">
+        <v>308</v>
+      </c>
+      <c r="F2" t="s">
         <v>282</v>
-      </c>
-      <c r="E2" t="s">
-        <v>309</v>
-      </c>
-      <c r="F2" t="s">
-        <v>283</v>
       </c>
       <c r="G2" t="s">
         <v>98</v>
       </c>
       <c r="I2" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="J2">
         <v>150</v>
       </c>
       <c r="P2" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q2" t="s">
         <v>89</v>
@@ -20821,10 +21980,13 @@
         <v>28</v>
       </c>
       <c r="U2" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="3" spans="1:22" x14ac:dyDescent="0.3">
+        <v>285</v>
+      </c>
+      <c r="X2" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="3" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -20832,31 +21994,31 @@
         <v>27</v>
       </c>
       <c r="C3" t="s">
+        <v>280</v>
+      </c>
+      <c r="D3" t="s">
         <v>281</v>
       </c>
-      <c r="D3" t="s">
+      <c r="E3" t="s">
+        <v>309</v>
+      </c>
+      <c r="F3" t="s">
         <v>282</v>
-      </c>
-      <c r="E3" t="s">
-        <v>310</v>
-      </c>
-      <c r="F3" t="s">
-        <v>283</v>
       </c>
       <c r="G3" t="s">
         <v>98</v>
       </c>
       <c r="H3" t="s">
+        <v>286</v>
+      </c>
+      <c r="I3" t="s">
         <v>287</v>
-      </c>
-      <c r="I3" t="s">
-        <v>288</v>
       </c>
       <c r="J3">
         <v>150</v>
       </c>
       <c r="P3" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q3" t="s">
         <v>89</v>
@@ -20868,10 +22030,13 @@
         <v>28</v>
       </c>
       <c r="U3" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="4" spans="1:22" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+      <c r="X3" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="4" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -20879,25 +22044,25 @@
         <v>27</v>
       </c>
       <c r="C4" t="s">
+        <v>280</v>
+      </c>
+      <c r="D4" t="s">
         <v>281</v>
       </c>
-      <c r="D4" t="s">
+      <c r="E4" t="s">
+        <v>309</v>
+      </c>
+      <c r="F4" t="s">
         <v>282</v>
-      </c>
-      <c r="E4" t="s">
-        <v>310</v>
-      </c>
-      <c r="F4" t="s">
-        <v>283</v>
       </c>
       <c r="G4" t="s">
         <v>98</v>
       </c>
       <c r="H4" t="s">
+        <v>286</v>
+      </c>
+      <c r="I4" t="s">
         <v>287</v>
-      </c>
-      <c r="I4" t="s">
-        <v>288</v>
       </c>
       <c r="J4">
         <v>150</v>
@@ -20906,7 +22071,7 @@
         <v>175</v>
       </c>
       <c r="P4" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q4" t="s">
         <v>89</v>
@@ -20918,10 +22083,13 @@
         <v>28</v>
       </c>
       <c r="U4" t="s">
-        <v>289</v>
-      </c>
-    </row>
-    <row r="5" spans="1:22" x14ac:dyDescent="0.3">
+        <v>288</v>
+      </c>
+      <c r="X4" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="5" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -20929,13 +22097,13 @@
         <v>27</v>
       </c>
       <c r="C5" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E5" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F5" t="s">
         <v>27</v>
@@ -20944,7 +22112,7 @@
         <v>98</v>
       </c>
       <c r="H5" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I5" t="s">
         <v>177</v>
@@ -20956,7 +22124,7 @@
         <v>175</v>
       </c>
       <c r="P5" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q5" t="s">
         <v>89</v>
@@ -20968,10 +22136,13 @@
         <v>28</v>
       </c>
       <c r="U5" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="6" spans="1:22" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+      <c r="X5" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="6" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -20979,13 +22150,13 @@
         <v>27</v>
       </c>
       <c r="C6" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="E6" t="s">
-        <v>293</v>
+        <v>292</v>
       </c>
       <c r="F6" t="s">
         <v>27</v>
@@ -21006,7 +22177,7 @@
         <v>175</v>
       </c>
       <c r="P6" t="s">
-        <v>306</v>
+        <v>305</v>
       </c>
       <c r="Q6" t="s">
         <v>89</v>
@@ -21018,10 +22189,13 @@
         <v>28</v>
       </c>
       <c r="U6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22" x14ac:dyDescent="0.3">
+        <v>293</v>
+      </c>
+      <c r="X6" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="7" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -21029,13 +22203,13 @@
         <v>27</v>
       </c>
       <c r="C7" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E7" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F7" t="s">
         <v>27</v>
@@ -21044,10 +22218,10 @@
         <v>98</v>
       </c>
       <c r="H7" t="s">
-        <v>295</v>
+        <v>294</v>
       </c>
       <c r="I7" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="J7">
         <v>35</v>
@@ -21068,10 +22242,13 @@
         <v>28</v>
       </c>
       <c r="U7" t="s">
-        <v>296</v>
-      </c>
-    </row>
-    <row r="8" spans="1:22" x14ac:dyDescent="0.3">
+        <v>295</v>
+      </c>
+      <c r="X7" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="8" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -21079,13 +22256,13 @@
         <v>27</v>
       </c>
       <c r="C8" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E8" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F8" t="s">
         <v>88</v>
@@ -21094,7 +22271,7 @@
         <v>98</v>
       </c>
       <c r="H8" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I8" t="s">
         <v>213</v>
@@ -21115,10 +22292,13 @@
         <v>28</v>
       </c>
       <c r="U8" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="9" spans="1:22" x14ac:dyDescent="0.3">
+        <v>296</v>
+      </c>
+      <c r="X8" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="9" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -21126,13 +22306,13 @@
         <v>27</v>
       </c>
       <c r="C9" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E9" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F9" t="s">
         <v>27</v>
@@ -21154,16 +22334,19 @@
         <v>28</v>
       </c>
       <c r="T9" t="s">
+        <v>298</v>
+      </c>
+      <c r="U9" t="s">
         <v>299</v>
-      </c>
-      <c r="U9" t="s">
-        <v>300</v>
       </c>
       <c r="V9" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="10" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X9" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="10" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -21171,13 +22354,13 @@
         <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E10" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F10" t="s">
         <v>27</v>
@@ -21198,16 +22381,19 @@
         <v>28</v>
       </c>
       <c r="T10" t="s">
+        <v>298</v>
+      </c>
+      <c r="U10" t="s">
         <v>299</v>
-      </c>
-      <c r="U10" t="s">
-        <v>300</v>
       </c>
       <c r="V10" t="s">
         <v>225</v>
       </c>
-    </row>
-    <row r="11" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X10" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="11" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>14</v>
       </c>
@@ -21215,13 +22401,13 @@
         <v>27</v>
       </c>
       <c r="C11" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="E11" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="F11" t="s">
         <v>27</v>
@@ -21230,7 +22416,7 @@
         <v>98</v>
       </c>
       <c r="H11" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="I11" t="s">
         <v>213</v>
@@ -21245,7 +22431,7 @@
         <v>175</v>
       </c>
       <c r="P11" t="s">
-        <v>285</v>
+        <v>284</v>
       </c>
       <c r="Q11" t="s">
         <v>89</v>
@@ -21257,10 +22443,13 @@
         <v>28</v>
       </c>
       <c r="U11" t="s">
-        <v>292</v>
-      </c>
-    </row>
-    <row r="12" spans="1:22" x14ac:dyDescent="0.3">
+        <v>291</v>
+      </c>
+      <c r="X11" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="12" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>15</v>
       </c>
@@ -21268,13 +22457,13 @@
         <v>27</v>
       </c>
       <c r="C12" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D12" t="s">
+        <v>300</v>
+      </c>
+      <c r="E12" t="s">
         <v>301</v>
-      </c>
-      <c r="E12" t="s">
-        <v>302</v>
       </c>
       <c r="F12" t="s">
         <v>27</v>
@@ -21287,13 +22476,16 @@
         <v>28</v>
       </c>
       <c r="U12" t="s">
+        <v>302</v>
+      </c>
+      <c r="V12" t="s">
         <v>303</v>
       </c>
-      <c r="V12" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="13" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X12" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="13" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>16</v>
       </c>
@@ -21301,31 +22493,34 @@
         <v>27</v>
       </c>
       <c r="C13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D13" t="s">
+        <v>300</v>
+      </c>
+      <c r="E13" t="s">
         <v>301</v>
       </c>
-      <c r="E13" t="s">
+      <c r="F13" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>89</v>
+      </c>
+      <c r="S13" t="s">
+        <v>28</v>
+      </c>
+      <c r="U13" t="s">
         <v>302</v>
       </c>
-      <c r="F13" t="s">
-        <v>27</v>
-      </c>
-      <c r="Q13" t="s">
-        <v>89</v>
-      </c>
-      <c r="S13" t="s">
-        <v>28</v>
-      </c>
-      <c r="U13" t="s">
+      <c r="V13" t="s">
         <v>303</v>
       </c>
-      <c r="V13" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="14" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X13" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="14" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>17</v>
       </c>
@@ -21333,18 +22528,18 @@
         <v>27</v>
       </c>
       <c r="C14" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D14" t="s">
+        <v>300</v>
+      </c>
+      <c r="E14" t="s">
         <v>301</v>
       </c>
-      <c r="E14" t="s">
-        <v>302</v>
-      </c>
       <c r="F14" t="s">
         <v>27</v>
       </c>
-      <c r="J14" s="16"/>
+      <c r="J14" s="15"/>
       <c r="Q14" t="s">
         <v>89</v>
       </c>
@@ -21355,13 +22550,16 @@
         <v>28</v>
       </c>
       <c r="U14" t="s">
+        <v>302</v>
+      </c>
+      <c r="V14" t="s">
         <v>303</v>
       </c>
-      <c r="V14" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="15" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X14" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="15" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>18</v>
       </c>
@@ -21369,13 +22567,13 @@
         <v>27</v>
       </c>
       <c r="C15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D15" t="s">
+        <v>300</v>
+      </c>
+      <c r="E15" t="s">
         <v>301</v>
-      </c>
-      <c r="E15" t="s">
-        <v>302</v>
       </c>
       <c r="F15" t="s">
         <v>27</v>
@@ -21390,13 +22588,16 @@
         <v>28</v>
       </c>
       <c r="U15" t="s">
+        <v>302</v>
+      </c>
+      <c r="V15" t="s">
         <v>303</v>
       </c>
-      <c r="V15" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="16" spans="1:22" x14ac:dyDescent="0.3">
+      <c r="X15" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="16" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>19</v>
       </c>
@@ -21404,13 +22605,13 @@
         <v>27</v>
       </c>
       <c r="C16" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D16" t="s">
+        <v>300</v>
+      </c>
+      <c r="E16" t="s">
         <v>301</v>
-      </c>
-      <c r="E16" t="s">
-        <v>302</v>
       </c>
       <c r="F16" t="s">
         <v>27</v>
@@ -21425,13 +22626,16 @@
         <v>28</v>
       </c>
       <c r="U16" t="s">
+        <v>302</v>
+      </c>
+      <c r="V16" t="s">
         <v>303</v>
       </c>
-      <c r="V16" t="s">
-        <v>304</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X16" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="17" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>20</v>
       </c>
@@ -21439,13 +22643,13 @@
         <v>27</v>
       </c>
       <c r="C17" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E17" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F17" t="s">
         <v>27</v>
@@ -21466,16 +22670,19 @@
         <v>28</v>
       </c>
       <c r="U17" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V17" t="s">
+        <v>303</v>
+      </c>
+      <c r="W17" t="s">
         <v>304</v>
       </c>
-      <c r="W17" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X17" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="18" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>21</v>
       </c>
@@ -21483,13 +22690,13 @@
         <v>27</v>
       </c>
       <c r="C18" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E18" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F18" t="s">
         <v>27</v>
@@ -21510,16 +22717,19 @@
         <v>28</v>
       </c>
       <c r="U18" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V18" t="s">
+        <v>303</v>
+      </c>
+      <c r="W18" t="s">
         <v>304</v>
       </c>
-      <c r="W18" t="s">
-        <v>305</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" x14ac:dyDescent="0.3">
+      <c r="X18" t="s">
+        <v>311</v>
+      </c>
+    </row>
+    <row r="19" spans="1:24" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>22</v>
       </c>
@@ -21527,13 +22737,13 @@
         <v>27</v>
       </c>
       <c r="C19" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="D19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="E19" t="s">
-        <v>298</v>
+        <v>297</v>
       </c>
       <c r="F19" t="s">
         <v>27</v>
@@ -21554,17 +22764,20 @@
         <v>28</v>
       </c>
       <c r="U19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="V19" t="s">
+        <v>303</v>
+      </c>
+      <c r="W19" t="s">
         <v>304</v>
       </c>
-      <c r="W19" t="s">
-        <v>305</v>
+      <c r="X19" t="s">
+        <v>311</v>
       </c>
     </row>
   </sheetData>
-  <dataValidations count="3">
+  <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="B2:B19" xr:uid="{2B6F0BAE-1307-4B1B-90C6-C1D65D2741DA}">
       <formula1>INDIRECT(A2 &amp; "_specs")</formula1>
     </dataValidation>
@@ -21573,6 +22786,9 @@
     </dataValidation>
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F2:F14" xr:uid="{562E144E-2576-46E1-B76C-317B450EC952}">
       <formula1>INDIRECT(D2 &amp; "_size")</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="X2:X23" xr:uid="{0714608B-3272-4EDB-A681-01011CAFDF01}">
+      <formula1>"LandLord , B&amp;Z"</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
